--- a/실습파일/실습1_행단위_병렬처리.xlsx
+++ b/실습파일/실습1_행단위_병렬처리.xlsx
@@ -587,7 +587,7 @@
     <row r="3">
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>걸리는 시간: 약 12분   ★ 40분 핵심 코스   |   [데이터] 탭 → [API 메뉴] → [DRM AI v10.0] → [Gemini 실행] 또는 [GPT 실행]</t>
+          <t>걸리는 시간: 약 12분   ★ 40분 핵심 코스   |   [데이터] 탭 → [API 메뉴] → [DRM AI v10.7] → [Gemini 실행] 또는 [GPT 실행]</t>
         </is>
       </c>
     </row>
@@ -702,14 +702,15 @@
     <row r="22" ht="32" customHeight="1">
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>③ 시작하면 멈출 수 없습니다. 실행이 시작된 뒤에는 ESC로 중단할 수 없습니다. 늘 3~5행만 먼저 돌려 보고 전체를 돌리세요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="32" customHeight="1">
+          <t>③ 시작하면 멈출 수 없습니다. 실행이 시작된 뒤에는 AI 처리를 ESC로 중단할 수 없습니다. 늘 3~5행만 먼저 돌려 보고 전체를 돌리세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="80" customHeight="1">
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>④ 선택한 칸의 내용은 AI 회사(구글·오픈AI) 서버로 전송됩니다. 학생 이름·학번·생기부 원문을 그대로 보내지 마세요. 실전에서는 이름 열을 빼고 필요한 내용만 보내면 됩니다.</t>
+          <t>④ 선택한 칸의 내용은 AI 회사(구글·오픈AI) 서버로 전송됩니다. 학생 이름·학번·생기부 원문을 그대로 보내지 마세요. 실전에서는 이름 열을 빼고 필요한 내용만 보내면 됩니다.
+행 단위 병렬 처리·절약 모드에서 글·PDF 첨부는 파일 이름을 AI 로 보내지 않고, 첫머리(앞 몇 줄)의 정해진 형식의 학번·이름만 가려 보냅니다. 스캔·사진·음성·동영상·손글씨·한글/워드 파일은 가려지지 않습니다. 셀에 적은 글은 그대로 가므로 이름 열은 여전히 빼세요.</t>
         </is>
       </c>
     </row>
@@ -731,7 +732,7 @@
     <row r="27" ht="34" customHeight="1">
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>2.  [데이터] 탭 → [API 메뉴] → [DRM AI v10.0] → [Gemini 실행] → [Gemini로 글과 파일(이미지, TXT, PDF, 음성 등) 행 단위 병렬 처리]</t>
+          <t>2.  [데이터] 탭 → [API 메뉴] → [DRM AI v10.7] → [Gemini 실행] → [Gemini로 글과 파일(이미지, TXT, PDF, 음성 등) 행 단위 병렬 처리]</t>
         </is>
       </c>
     </row>
